--- a/artfynd/A 52210-2022 artfynd.xlsx
+++ b/artfynd/A 52210-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52210-2022 artfynd.xlsx
+++ b/artfynd/A 52210-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5338,6 +5338,108 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120108356</v>
+      </c>
+      <c r="B39" t="n">
+        <v>96862</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Krampdalsbron, Krampdalsbron, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>507935</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6601737</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52210-2022 artfynd.xlsx
+++ b/artfynd/A 52210-2022 artfynd.xlsx
@@ -5343,7 +5343,7 @@
         <v>120108356</v>
       </c>
       <c r="B39" t="n">
-        <v>96862</v>
+        <v>96885</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
